--- a/output/pdf_financials_xlsx/GAU.xlsx
+++ b/output/pdf_financials_xlsx/GAU.xlsx
@@ -1309,25 +1309,25 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>4.316042</v>
+        <v>-4.316042</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>4.176396</v>
+        <v>-4.176396</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>6.972686</v>
+        <v>-6.972686</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>34.852715</v>
+        <v>-34.852715</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>13.546202</v>
+        <v>-13.546202</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.692203</v>
+        <v>-1.692203</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>20.291</v>
+        <v>-24.993</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-11.29</v>
@@ -1625,25 +1625,25 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>4.316042</v>
+        <v>-4.316042</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4.176396</v>
+        <v>-4.176396</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>6.972686</v>
+        <v>-6.972686</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>34.852715</v>
+        <v>-34.852715</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>13.546202</v>
+        <v>-13.546202</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.692203</v>
+        <v>-1.692203</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>22.642</v>
+        <v>-22.642</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-8.305999999999999</v>
@@ -1808,25 +1808,25 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>4.316042</v>
+        <v>-4.316042</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>4.176396</v>
+        <v>-4.176396</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>6.972686</v>
+        <v>-6.972686</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>34.852715</v>
+        <v>-34.852715</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>13.546202</v>
+        <v>-13.546202</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.692203</v>
+        <v>-1.692203</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>22.642</v>
+        <v>-22.642</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-8.305999999999999</v>
@@ -2019,25 +2019,25 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>25.388482</v>
+        <v>-25.388482</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>27.84264</v>
+        <v>-27.84264</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>38.737144</v>
+        <v>-38.737144</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>49.088331</v>
+        <v>-49.088331</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>79.68354100000001</v>
+        <v>-79.68354100000001</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>84.61015</v>
+        <v>-84.61015</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>161.728571</v>
+        <v>-161.728571</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>207.65</v>
@@ -2080,25 +2080,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>4.316042</v>
+        <v>-4.316042</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4.176396</v>
+        <v>-4.176396</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>6.972686</v>
+        <v>-6.972686</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>34.852715</v>
+        <v>-34.852715</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>13.546202</v>
+        <v>-13.546202</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.692203</v>
+        <v>-1.692203</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>20.291</v>
+        <v>-24.993</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-12.305</v>
@@ -2202,25 +2202,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>4.316042</v>
+        <v>-4.316042</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4.176396</v>
+        <v>-4.176396</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>6.972686</v>
+        <v>-6.972686</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>34.852715</v>
+        <v>-34.852715</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>13.819024</v>
+        <v>-13.27338</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.841899</v>
+        <v>-1.542507</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>20.445</v>
+        <v>-24.839</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-12.246</v>
@@ -2350,25 +2350,25 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>11.58641762357696</v>
+        <v>-9.406633857480093</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-26.43046944198406</v>
@@ -6628,13 +6628,13 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>4.316042</v>
+        <v>-4.316042</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>4.176396</v>
+        <v>-4.176396</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>6.972686</v>
+        <v>-6.972686</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-34.852715</v>
@@ -7796,19 +7796,19 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>3.296932</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>0.309251</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>0.032637</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>0.242</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
@@ -52556,7 +52556,11 @@
           <t>Share-based payments included in exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -58528,7 +58532,11 @@
           <t>Share-based compensation included in exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E474" t="inlineStr">
         <is>
           <t>-</t>
@@ -86160,10 +86168,10 @@
         </is>
       </c>
       <c r="K737" s="5" t="n">
-        <v>22.642</v>
+        <v>-22.642</v>
       </c>
       <c r="L737" s="5" t="n">
-        <v>8.305999999999999</v>
+        <v>-8.305999999999999</v>
       </c>
       <c r="M737" t="inlineStr">
         <is>
@@ -88477,10 +88485,10 @@
         </is>
       </c>
       <c r="J759" s="5" t="n">
-        <v>1.692203</v>
+        <v>-1.692203</v>
       </c>
       <c r="K759" s="5" t="n">
-        <v>22.641634</v>
+        <v>-22.641634</v>
       </c>
       <c r="L759" t="inlineStr">
         <is>
@@ -89934,10 +89942,10 @@
         </is>
       </c>
       <c r="I773" s="5" t="n">
-        <v>13.546202</v>
+        <v>-13.546202</v>
       </c>
       <c r="J773" s="5" t="n">
-        <v>1.692203</v>
+        <v>-1.692203</v>
       </c>
       <c r="K773" t="inlineStr">
         <is>
@@ -91521,10 +91529,10 @@
         </is>
       </c>
       <c r="H788" s="5" t="n">
-        <v>34.852715</v>
+        <v>-34.852715</v>
       </c>
       <c r="I788" s="5" t="n">
-        <v>38.152585</v>
+        <v>-38.152585</v>
       </c>
       <c r="J788" t="inlineStr">
         <is>
@@ -93184,13 +93192,13 @@
         </is>
       </c>
       <c r="E804" s="5" t="n">
-        <v>4.316042</v>
+        <v>-4.316042</v>
       </c>
       <c r="F804" s="5" t="n">
-        <v>4.176396</v>
+        <v>-4.176396</v>
       </c>
       <c r="G804" s="5" t="n">
-        <v>6.972686</v>
+        <v>-6.972686</v>
       </c>
       <c r="H804" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GAU.xlsx
+++ b/output/pdf_financials_xlsx/GAU.xlsx
@@ -1113,10 +1113,10 @@
         <v>6.255</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>5.853</v>
+        <v>4.707</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>6.056</v>
+        <v>3.412</v>
       </c>
     </row>
     <row r="13">
@@ -2128,10 +2128,10 @@
         <v>19.83</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>2.688</v>
+        <v>3.834</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>24.426</v>
+        <v>27.07</v>
       </c>
     </row>
     <row r="28">
@@ -2250,10 +2250,10 @@
         <v>19.973</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>2.688</v>
+        <v>3.834</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>24.426</v>
+        <v>27.07</v>
       </c>
     </row>
     <row r="30">
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="R30" s="3" t="n">
-        <v>1.161931191887231</v>
+        <v>1.657308106285581</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>5.455069265935185</v>
+        <v>6.045554942637577</v>
       </c>
     </row>
     <row r="31">
@@ -8195,16 +8195,16 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.117</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.128</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.127</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -8256,16 +8256,16 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.117</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.128</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.127</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>0</v>
@@ -20330,7 +20330,11 @@
           <t>Reclamation deposit 22</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -22038,7 +22042,11 @@
           <t>Reclamation deposit 16</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -24248,7 +24256,11 @@
           <t>Reclamation deposit 14</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -25934,7 +25946,11 @@
           <t>Reclamation deposit (note 7)</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -40816,7 +40832,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -42466,7 +42486,11 @@
           <t>Office lease payments</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -66166,7 +66190,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">

--- a/output/pdf_financials_xlsx/GAU.xlsx
+++ b/output/pdf_financials_xlsx/GAU.xlsx
@@ -7433,10 +7433,10 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.007371</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.055327</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -56030,7 +56030,11 @@
           <t>Proceeds from disposal of plant and equipment</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
